--- a/data/trans_dic/P32E$calle_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,27</t>
+          <t>0,0; 25,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,34</t>
+          <t>0,0; 18,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,71; 60,05</t>
+          <t>20,21; 60,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,84</t>
+          <t>0,0; 65,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,79; 54,78</t>
+          <t>20,88; 53,97</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 25,71</t>
+          <t>2,79; 25,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 68,74</t>
+          <t>11,9; 70,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,85; 35,89</t>
+          <t>8,19; 35,32</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,0; 46,52</t>
+          <t>16,01; 47,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 39,39</t>
+          <t>3,33; 43,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,9; 40,08</t>
+          <t>15,01; 41,56</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,83; 28,73</t>
+          <t>12,26; 28,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,39; 33,8</t>
+          <t>7,9; 34,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,9; 25,32</t>
+          <t>13,28; 25,86</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1256</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1289</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2368</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2262</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3341</t>
+          <t>0; 3801</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4051</t>
+          <t>0; 2990</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1496</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1842</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1135</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 310</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 948</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5685; 16485</t>
+          <t>5547; 16657</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4637</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6826; 18896</t>
+          <t>7201; 18618</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>887; 8472</t>
+          <t>920; 8336</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1694; 10511</t>
+          <t>1820; 10831</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3787; 17314</t>
+          <t>3950; 17040</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6742; 19596</t>
+          <t>6744; 19993</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>534; 6277</t>
+          <t>531; 6903</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8068; 23269</t>
+          <t>8717; 24128</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18488; 41401</t>
+          <t>17661; 40750</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4589; 18495</t>
+          <t>4325; 18671</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25652; 50338</t>
+          <t>26403; 51410</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$calle_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Provincia-trans_dic.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,34</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,7</t>
+          <t>0,0; 19,29</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,21; 60,67</t>
+          <t>18,47; 56,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,87</t>
+          <t>0,0; 68,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,88; 53,97</t>
+          <t>19,37; 51,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,3</t>
+          <t>2,34; 20,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,9; 70,83</t>
+          <t>7,15; 58,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,19; 35,32</t>
+          <t>5,74; 28,56</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,01; 47,47</t>
+          <t>16,91; 47,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 43,32</t>
+          <t>3,11; 40,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,01; 41,56</t>
+          <t>14,7; 40,22</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,26; 28,28</t>
+          <t>11,7; 25,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,9; 34,12</t>
+          <t>7,73; 28,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,28; 25,86</t>
+          <t>12,23; 23,78</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3801</t>
+          <t>0; 3789</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2990</t>
+          <t>0; 3313</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>11830</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5547; 16657</t>
+          <t>5041; 15504</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>0; 4882</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7201; 18618</t>
+          <t>6668; 17810</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9014</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>920; 8336</t>
+          <t>1027; 9032</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1820; 10831</t>
+          <t>1406; 11491</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3950; 17040</t>
+          <t>3649; 18150</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>16810</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6744; 19993</t>
+          <t>7907; 22156</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>531; 6903</t>
+          <t>575; 7454</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8717; 24128</t>
+          <t>9589; 26240</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17661; 40750</t>
+          <t>18895; 41745</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4325; 18671</t>
+          <t>4961; 18216</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26403; 51410</t>
+          <t>27593; 53671</t>
         </is>
       </c>
     </row>
